--- a/metrics/extension-untracked-2026-03-20.xlsx
+++ b/metrics/extension-untracked-2026-03-20.xlsx
@@ -54,7 +54,7 @@
     <t>medium</t>
   </si>
   <si>
-    <t>../../components/app/preferred-avatar, ../../../components/app/preferred-avatar, ../../app/preferred-avatar, ../preferred-avatar, ../preferred-avatar/preferred-avatar, ../../../../components/app/preferred-avatar, ../../../app/preferred-avatar, ../../preferred-avatar, ../../../../../components/app/preferred-avatar, ../../../preferred-avatar, ../../../../app/preferred-avatar, ../../../../../../components/app/preferred-avatar, ../../../../../../../components/app/preferred-avatar</t>
+    <t>../../components/app/preferred-avatar, ../../../components/app/preferred-avatar, ../../app/preferred-avatar, ../preferred-avatar, ../preferred-avatar/preferred-avatar, ../../../../components/app/preferred-avatar, ../../../app/preferred-avatar, ../../preferred-avatar, ../../../../../components/app/preferred-avatar, ../../../../app/preferred-avatar, ../../../preferred-avatar, ../../../../../../components/app/preferred-avatar, ../../../../../../../components/app/preferred-avatar</t>
   </si>
   <si>
     <t>ToggleButton</t>
@@ -93,7 +93,7 @@
     <t>AvatarNetwork</t>
   </si>
   <si>
-    <t>./network-list-item/network-list-item, ../network-list-item, ../../../../components/multichain/network-list-item, ../../../multichain/network-list-item, ../../network-list-item, ../../../../../components/multichain, ../../../network-list-item</t>
+    <t>../network-list-item, ./network-list-item/network-list-item, ../../../../components/multichain/network-list-item, ../../../multichain/network-list-item, ../../network-list-item, ../../../../../components/multichain, ../../../network-list-item</t>
   </si>
   <si>
     <t>../../components/ui/button, ../../../components/ui/button, ../button, ../../ui/button, ../../button</t>
@@ -111,7 +111,7 @@
     <t>Icon</t>
   </si>
   <si>
-    <t>../../components/app/snaps/snap-icon, ../snaps/snap-icon, ../../app/snaps/snap-icon, ../../../../components/app/snaps/snap-icon, ../snap-icon, ../../../app/snaps/snap-icon</t>
+    <t>../../components/app/snaps/snap-icon, ../../app/snaps/snap-icon, ../snaps/snap-icon, ../../../../components/app/snaps/snap-icon, ../../../app/snaps/snap-icon, ../snap-icon</t>
   </si>
   <si>
     <t>RewardsBadge</t>
@@ -141,7 +141,7 @@
     <t>BadgeStatus</t>
   </si>
   <si>
-    <t>../transaction-status-label/transaction-status-label, ../../app/transaction-status-label/transaction-status-label</t>
+    <t>../../app/transaction-status-label/transaction-status-label, ../transaction-status-label/transaction-status-label</t>
   </si>
   <si>
     <t>AccountDetailsRow</t>
@@ -174,7 +174,7 @@
     <t>AvatarGroup</t>
   </si>
   <si>
-    <t>../../multichain/avatar-group, ../avatar-group, ../../../../multichain/avatar-group/avatar-group, ../../.., ../../../avatar-group</t>
+    <t>../../multichain/avatar-group, ../avatar-group, ../../.., ../../../avatar-group, ../../../../multichain/avatar-group/avatar-group</t>
   </si>
   <si>
     <t>AccountListItem</t>
@@ -189,16 +189,16 @@
     <t/>
   </si>
   <si>
+    <t>NotificationDetailCopyButton</t>
+  </si>
+  <si>
+    <t>../notification-detail-copy-button, ../../../../components/multichain</t>
+  </si>
+  <si>
     <t>TransactionIcon</t>
   </si>
   <si>
-    <t>../transaction-icon, ../../app/transaction-icon/transaction-icon</t>
-  </si>
-  <si>
-    <t>NotificationDetailCopyButton</t>
-  </si>
-  <si>
-    <t>../notification-detail-copy-button, ../../../../components/multichain</t>
+    <t>../../app/transaction-icon/transaction-icon, ../transaction-icon</t>
   </si>
   <si>
     <t>NotificationDetailNetworkFee</t>
@@ -243,30 +243,30 @@
     <t>../../../components/app/assets/stock-badge/stock-badge, ../../app/assets/stock-badge/stock-badge, ../../../../../components/app/assets/stock-badge/stock-badge, ../../stock-badge/stock-badge</t>
   </si>
   <si>
+    <t>NotificationDetailButton</t>
+  </si>
+  <si>
+    <t>../notification-detail-button, ../../../../components/multichain</t>
+  </si>
+  <si>
+    <t>CreateSnapAccount</t>
+  </si>
+  <si>
+    <t>../create-snap-account/create-snap-account, ../create-snap-account, ../../create-snap-account</t>
+  </si>
+  <si>
+    <t>ChainBadge</t>
+  </si>
+  <si>
+    <t>../../app/chain-badge/chain-badge, ../chain-badge/chain-badge</t>
+  </si>
+  <si>
     <t>CancelButton</t>
   </si>
   <si>
     <t>../cancel-button</t>
   </si>
   <si>
-    <t>ChainBadge</t>
-  </si>
-  <si>
-    <t>../chain-badge/chain-badge, ../../app/chain-badge/chain-badge</t>
-  </si>
-  <si>
-    <t>NotificationDetailButton</t>
-  </si>
-  <si>
-    <t>../notification-detail-button, ../../../../components/multichain</t>
-  </si>
-  <si>
-    <t>CreateSnapAccount</t>
-  </si>
-  <si>
-    <t>../create-snap-account/create-snap-account, ../create-snap-account, ../../create-snap-account</t>
-  </si>
-  <si>
     <t>MultipleAlertModal</t>
   </si>
   <si>
@@ -321,16 +321,34 @@
     <t>../../../components/ui/check-box, ../../ui/check-box, ../../../ui/check-box</t>
   </si>
   <si>
+    <t>IconWithFallback</t>
+  </si>
+  <si>
+    <t>../icon-with-fallback, ../../ui/icon-with-fallback</t>
+  </si>
+  <si>
     <t>MultichainAccountNetworkGroup</t>
   </si>
   <si>
     <t>../multichain-account-network-group, ../../multichain-accounts/multichain-account-network-group</t>
   </si>
   <si>
-    <t>IconWithFallback</t>
-  </si>
-  <si>
-    <t>../icon-with-fallback, ../../ui/icon-with-fallback</t>
+    <t>NotificationListItemText</t>
+  </si>
+  <si>
+    <t>../notification-list-item-text</t>
+  </si>
+  <si>
+    <t>NetworkFilter</t>
+  </si>
+  <si>
+    <t>../../app/assets/asset-list/network-filter, ../../assets/asset-list/network-filter, ../network-filter</t>
+  </si>
+  <si>
+    <t>AccountOverviewLayout</t>
+  </si>
+  <si>
+    <t>./account-overview-layout</t>
   </si>
   <si>
     <t>AccountRow</t>
@@ -339,24 +357,6 @@
     <t>../../rows/account-row</t>
   </si>
   <si>
-    <t>NotificationListItemText</t>
-  </si>
-  <si>
-    <t>../notification-list-item-text</t>
-  </si>
-  <si>
-    <t>NetworkFilter</t>
-  </si>
-  <si>
-    <t>../../app/assets/asset-list/network-filter, ../../assets/asset-list/network-filter, ../network-filter</t>
-  </si>
-  <si>
-    <t>AccountOverviewLayout</t>
-  </si>
-  <si>
-    <t>./account-overview-layout</t>
-  </si>
-  <si>
     <t>SnapUIAvatar</t>
   </si>
   <si>
@@ -504,6 +504,18 @@
     <t>../../../components/app/wallet-overview/coin-buttons, ./coin-buttons</t>
   </si>
   <si>
+    <t>AccountMismatchWarning</t>
+  </si>
+  <si>
+    <t>../account-mismatch-warning/account-mismatch-warning.component, ../../ui/account-mismatch-warning/account-mismatch-warning.component</t>
+  </si>
+  <si>
+    <t>InfoTooltipIcon</t>
+  </si>
+  <si>
+    <t>./info-tooltip-icon, ../info-tooltip/info-tooltip-icon</t>
+  </si>
+  <si>
     <t>ConnectedStatus</t>
   </si>
   <si>
@@ -525,16 +537,52 @@
     <t>../../multichain/account-details/account-details-key, ./account-details-key</t>
   </si>
   <si>
-    <t>AccountMismatchWarning</t>
-  </si>
-  <si>
-    <t>../account-mismatch-warning/account-mismatch-warning.component, ../../ui/account-mismatch-warning/account-mismatch-warning.component</t>
-  </si>
-  <si>
-    <t>InfoTooltipIcon</t>
-  </si>
-  <si>
-    <t>./info-tooltip-icon, ../info-tooltip/info-tooltip-icon</t>
+    <t>AddNetwork</t>
+  </si>
+  <si>
+    <t>./components/add-network</t>
+  </si>
+  <si>
+    <t>NetworkSelectorCustomImport</t>
+  </si>
+  <si>
+    <t>../../app/import-token/network-selector-custom-import</t>
+  </si>
+  <si>
+    <t>TokenListPlaceholder</t>
+  </si>
+  <si>
+    <t>../../app/import-token/token-list/token-list-placeholder, ./token-list-placeholder</t>
+  </si>
+  <si>
+    <t>TokenList</t>
+  </si>
+  <si>
+    <t>../../app/import-token/token-list, ../token-list</t>
+  </si>
+  <si>
+    <t>BottomButtons</t>
+  </si>
+  <si>
+    <t>./bottom-buttons</t>
+  </si>
+  <si>
+    <t>CreateEthAccount</t>
+  </si>
+  <si>
+    <t>../create-eth-account</t>
+  </si>
+  <si>
+    <t>CreateAccount</t>
+  </si>
+  <si>
+    <t>../create-account</t>
+  </si>
+  <si>
+    <t>AccountDetailsSection</t>
+  </si>
+  <si>
+    <t>./account-details-section</t>
   </si>
   <si>
     <t>SwitchToInfuraButton</t>
@@ -555,54 +603,6 @@
     <t>./recipient-group/recipient-group.component</t>
   </si>
   <si>
-    <t>AddNetwork</t>
-  </si>
-  <si>
-    <t>./components/add-network</t>
-  </si>
-  <si>
-    <t>NetworkSelectorCustomImport</t>
-  </si>
-  <si>
-    <t>../../app/import-token/network-selector-custom-import</t>
-  </si>
-  <si>
-    <t>TokenListPlaceholder</t>
-  </si>
-  <si>
-    <t>../../app/import-token/token-list/token-list-placeholder, ./token-list-placeholder</t>
-  </si>
-  <si>
-    <t>TokenList</t>
-  </si>
-  <si>
-    <t>../../app/import-token/token-list, ../token-list</t>
-  </si>
-  <si>
-    <t>BottomButtons</t>
-  </si>
-  <si>
-    <t>./bottom-buttons</t>
-  </si>
-  <si>
-    <t>CreateEthAccount</t>
-  </si>
-  <si>
-    <t>../create-eth-account</t>
-  </si>
-  <si>
-    <t>CreateAccount</t>
-  </si>
-  <si>
-    <t>../create-account</t>
-  </si>
-  <si>
-    <t>AccountDetailsSection</t>
-  </si>
-  <si>
-    <t>./account-details-section</t>
-  </si>
-  <si>
     <t>InlineAlert</t>
   </si>
   <si>
@@ -639,6 +639,12 @@
     <t>../avatar-group/multichain-avatar-group</t>
   </si>
   <si>
+    <t>TokenListItem</t>
+  </si>
+  <si>
+    <t>../../token-list-item</t>
+  </si>
+  <si>
     <t>RewardsErrorBanner</t>
   </si>
   <si>
@@ -675,12 +681,6 @@
     <t>../alert-modal/alert-modal</t>
   </si>
   <si>
-    <t>TokenListItem</t>
-  </si>
-  <si>
-    <t>../../token-list-item</t>
-  </si>
-  <si>
     <t>GasInput</t>
   </si>
   <si>
@@ -711,15 +711,15 @@
     <t>../transaction-status-icon</t>
   </si>
   <si>
+    <t>CopyIcon</t>
+  </si>
+  <si>
+    <t>../../../../app/confirm/info/row/copy-icon, ./copy-icon</t>
+  </si>
+  <si>
     <t>InfoText</t>
   </si>
   <si>
-    <t>CopyIcon</t>
-  </si>
-  <si>
-    <t>./copy-icon, ../../../../app/confirm/info/row/copy-icon</t>
-  </si>
-  <si>
     <t>AdvancedGasFeeInputSubtext</t>
   </si>
   <si>
@@ -735,7 +735,7 @@
     <t>Tooltip</t>
   </si>
   <si>
-    <t>../../components/ui/tooltip, ../../../components/ui/tooltip, react-tippy, ../layout, ../tooltip, ../tooltip/tooltip, ../../ui/tooltip, @material-ui/core/Tooltip, ../../ui/tooltip/tooltip, ../../../../components/ui/tooltip, ../../../../components/ui/tooltip/tooltip, ../../../ui/tooltip, ../../../ui/tooltip/tooltip, ../../../../../components/ui/tooltip, ../../../../../components/ui/tooltip/tooltip, ../../../../ui/tooltip, ../../../../ui/tooltip/tooltip, ../../../../../../components/ui/tooltip, ../../../../../../../components/ui/tooltip, ../../../../../../../../components/ui/tooltip</t>
+    <t>../../components/ui/tooltip, ../../../components/ui/tooltip, react-tippy, ../layout, ../tooltip, ../tooltip/tooltip, ../../ui/tooltip, ../../ui/tooltip/tooltip, @material-ui/core/Tooltip, ../../../../components/ui/tooltip, ../../../../components/ui/tooltip/tooltip, ../../../ui/tooltip, ../../../ui/tooltip/tooltip, ../../../../../components/ui/tooltip, ../../../../../components/ui/tooltip/tooltip, ../../../../ui/tooltip, ../../../../ui/tooltip/tooltip, ../../../../../../components/ui/tooltip, ../../../../../../../components/ui/tooltip, ../../../../../../../../components/ui/tooltip</t>
   </si>
   <si>
     <t>ConfirmInfoRow</t>
@@ -759,13 +759,13 @@
     <t>Header</t>
   </si>
   <si>
-    <t>../../components/multichain/pages/page, ../../../components/multichain/pages/page, ../components/send/header, ../components/confirm/header, ../pages/page, ../../../multichain/pages/page, ../page, ../../../../multichain/pages/page, ../../page</t>
+    <t>../../components/multichain/pages/page, ../../../components/multichain/pages/page, ../components/send/header, ../components/confirm/header, ../pages/page, ../../../multichain/pages/page, ../page, ../../page, ../../../../multichain/pages/page</t>
   </si>
   <si>
     <t>Page</t>
   </si>
   <si>
-    <t>../../components/multichain/pages/page, ../../../components/multichain/pages/page, ../../../multichain/pages/page, ../page, ../../../../multichain/pages/page, ../../page</t>
+    <t>../../components/multichain/pages/page, ../../../components/multichain/pages/page, ../../../multichain/pages/page, ../page, ../../page, ../../../../multichain/pages/page</t>
   </si>
   <si>
     <t>Toast</t>
@@ -786,7 +786,7 @@
     <t>UserPreferencedCurrencyDisplay</t>
   </si>
   <si>
-    <t>../user-preferenced-currency-display, ../../app/user-preferenced-currency-display/user-preferenced-currency-display.component, ../../../../components/app/user-preferenced-currency-display, ../../../../components/app/user-preferenced-currency-display/user-preferenced-currency-display.component, ../../../app/user-preferenced-currency-display/user-preferenced-currency-display.component, ../../../../../components/app/user-preferenced-currency-display, ../../../user-preferenced-currency-display, ../../../user-preferenced-currency-display/user-preferenced-currency-display.component</t>
+    <t>../../app/user-preferenced-currency-display/user-preferenced-currency-display.component, ../user-preferenced-currency-display, ../../../../components/app/user-preferenced-currency-display, ../../../../components/app/user-preferenced-currency-display/user-preferenced-currency-display.component, ../../../app/user-preferenced-currency-display/user-preferenced-currency-display.component, ../../../../../components/app/user-preferenced-currency-display, ../../../user-preferenced-currency-display, ../../../user-preferenced-currency-display/user-preferenced-currency-display.component</t>
   </si>
   <si>
     <t>Column</t>
@@ -828,7 +828,7 @@
     <t>Preloader</t>
   </si>
   <si>
-    <t>../../components/ui/icon/preloader/preloader-icon.component, ../../ui/icon/preloader, ../icon/preloader/preloader-icon.component, ../../ui/icon/preloader/preloader-icon.component, ../../../ui/icon/preloader/preloader-icon.component, ../../../../../components/ui/icon/preloader, ../../../../../../components/ui/icon/preloader, ../../../../../../../components/ui/icon/preloader</t>
+    <t>../../components/ui/icon/preloader/preloader-icon.component, ../icon/preloader/preloader-icon.component, ../../ui/icon/preloader, ../../ui/icon/preloader/preloader-icon.component, ../../../ui/icon/preloader/preloader-icon.component, ../../../../../components/ui/icon/preloader, ../../../../../../components/ui/icon/preloader, ../../../../../../../components/ui/icon/preloader</t>
   </si>
   <si>
     <t>TransactionBreakdownRow</t>
@@ -1233,13 +1233,13 @@
     <t>ActivityListItem</t>
   </si>
   <si>
-    <t>../../multichain/activity-list-item, ../../multichain/activity-list-item/activity-list-item, ./activity-list-item</t>
+    <t>./activity-list-item, ../../multichain/activity-list-item, ../../multichain/activity-list-item/activity-list-item</t>
   </si>
   <si>
     <t>AssetListControlBar</t>
   </si>
   <si>
-    <t>../../app/assets/asset-list/asset-list-control-bar, ../asset-list/asset-list-control-bar, ./asset-list-control-bar, ../../asset-list/asset-list-control-bar</t>
+    <t>../../app/assets/asset-list/asset-list-control-bar, ./asset-list-control-bar, ../asset-list/asset-list-control-bar, ../../asset-list/asset-list-control-bar</t>
   </si>
   <si>
     <t>ClaimsForm</t>
@@ -1293,16 +1293,22 @@
     <t>FoxAppearAnimation</t>
   </si>
   <si>
+    <t>RouterRoutes</t>
+  </si>
+  <si>
+    <t>react-router-dom</t>
+  </si>
+  <si>
     <t>ApiErrorHandler</t>
   </si>
   <si>
     <t>../../components/app/api-error-handler, ../../../components/app/api-error-handler, ../../../../components/app/api-error-handler</t>
   </si>
   <si>
-    <t>RouterRoutes</t>
-  </si>
-  <si>
-    <t>react-router-dom</t>
+    <t>Loading</t>
+  </si>
+  <si>
+    <t>../../components/ui/loading-screen, ../../../components/ui/loading-screen</t>
   </si>
   <si>
     <t>PasswordOutdatedModal</t>
@@ -1311,12 +1317,6 @@
     <t>../../components/app/password-outdated-modal, ../../../components/app/password-outdated-modal</t>
   </si>
   <si>
-    <t>Loading</t>
-  </si>
-  <si>
-    <t>../../components/ui/loading-screen, ../../../components/ui/loading-screen</t>
-  </si>
-  <si>
     <t>ErrorContent</t>
   </si>
   <si>
@@ -1368,66 +1368,66 @@
     <t>../components/gas-timing/gas-timing.component, ../gas-timing/gas-timing.component, ../../../../gas-timing/gas-timing.component</t>
   </si>
   <si>
+    <t>StakeableLink</t>
+  </si>
+  <si>
+    <t>./stakeable-link, ../../../../multichain/token-list-item/stakeable-link</t>
+  </si>
+  <si>
+    <t>QrCodeView</t>
+  </si>
+  <si>
+    <t>../../ui/qr-code-view</t>
+  </si>
+  <si>
+    <t>AddRpcUrlModal</t>
+  </si>
+  <si>
+    <t>../network-list-menu/add-rpc-url-modal/add-rpc-url-modal, ./add-rpc-url-modal/add-rpc-url-modal</t>
+  </si>
+  <si>
+    <t>AddBlockExplorerModal</t>
+  </si>
+  <si>
+    <t>../network-list-menu/add-block-explorer-modal/add-block-explorer-modal, ./add-block-explorer-modal/add-block-explorer-modal</t>
+  </si>
+  <si>
+    <t>FundingMethodItem</t>
+  </si>
+  <si>
+    <t>./funding-method-item</t>
+  </si>
+  <si>
+    <t>Confusable</t>
+  </si>
+  <si>
+    <t>../../ui/confusable</t>
+  </si>
+  <si>
+    <t>CSSTransitionComponent</t>
+  </si>
+  <si>
+    <t>react-transition-group</t>
+  </si>
+  <si>
+    <t>AssetList</t>
+  </si>
+  <si>
+    <t>../../app/assets/asset-list, ./AssetList, ../asset-list</t>
+  </si>
+  <si>
     <t>HexToDecimal</t>
   </si>
   <si>
     <t>../../ui/hex-to-decimal</t>
   </si>
   <si>
-    <t>QrCodeView</t>
-  </si>
-  <si>
-    <t>../../ui/qr-code-view</t>
-  </si>
-  <si>
     <t>PermissionCell</t>
   </si>
   <si>
     <t>../permission-cell, ../../permission-cell</t>
   </si>
   <si>
-    <t>StakeableLink</t>
-  </si>
-  <si>
-    <t>./stakeable-link, ../../../../multichain/token-list-item/stakeable-link</t>
-  </si>
-  <si>
-    <t>AddRpcUrlModal</t>
-  </si>
-  <si>
-    <t>../network-list-menu/add-rpc-url-modal/add-rpc-url-modal, ./add-rpc-url-modal/add-rpc-url-modal</t>
-  </si>
-  <si>
-    <t>AddBlockExplorerModal</t>
-  </si>
-  <si>
-    <t>../network-list-menu/add-block-explorer-modal/add-block-explorer-modal, ./add-block-explorer-modal/add-block-explorer-modal</t>
-  </si>
-  <si>
-    <t>FundingMethodItem</t>
-  </si>
-  <si>
-    <t>./funding-method-item</t>
-  </si>
-  <si>
-    <t>Confusable</t>
-  </si>
-  <si>
-    <t>../../ui/confusable</t>
-  </si>
-  <si>
-    <t>CSSTransitionComponent</t>
-  </si>
-  <si>
-    <t>react-transition-group</t>
-  </si>
-  <si>
-    <t>AssetList</t>
-  </si>
-  <si>
-    <t>../../app/assets/asset-list, ./AssetList, ../asset-list</t>
-  </si>
-  <si>
     <t>ToggleArrows</t>
   </si>
   <si>
@@ -1488,30 +1488,30 @@
     <t>../../modal</t>
   </si>
   <si>
+    <t>PayWithRow</t>
+  </si>
+  <si>
+    <t>../pay-with-row/pay-with-row, ../../rows/pay-with-row/pay-with-row</t>
+  </si>
+  <si>
+    <t>BridgeFeeRow</t>
+  </si>
+  <si>
+    <t>../bridge-fee-row/bridge-fee-row, ../../rows/bridge-fee-row/bridge-fee-row</t>
+  </si>
+  <si>
+    <t>TotalRow</t>
+  </si>
+  <si>
+    <t>../total-row/total-row, ../../rows/total-row/total-row</t>
+  </si>
+  <si>
     <t>Recipient</t>
   </si>
   <si>
     <t>../../UI/recipient, ../recipient</t>
   </si>
   <si>
-    <t>PayWithRow</t>
-  </si>
-  <si>
-    <t>../pay-with-row/pay-with-row, ../../rows/pay-with-row/pay-with-row</t>
-  </si>
-  <si>
-    <t>BridgeFeeRow</t>
-  </si>
-  <si>
-    <t>../bridge-fee-row/bridge-fee-row, ../../rows/bridge-fee-row/bridge-fee-row</t>
-  </si>
-  <si>
-    <t>TotalRow</t>
-  </si>
-  <si>
-    <t>../total-row/total-row, ../../rows/total-row/total-row</t>
-  </si>
-  <si>
     <t>DataTree</t>
   </si>
   <si>
@@ -1584,18 +1584,18 @@
     <t>../../components/app/srp-details-modal, ../../../components/app/srp-details-modal</t>
   </si>
   <si>
+    <t>TabBar</t>
+  </si>
+  <si>
+    <t>../../components/app/tab-bar</t>
+  </si>
+  <si>
     <t>ShieldPaymentModal</t>
   </si>
   <si>
     <t>./shield-payment-modal, ../../shield-plan/shield-payment-modal</t>
   </si>
   <si>
-    <t>TabBar</t>
-  </si>
-  <si>
-    <t>../../components/app/tab-bar</t>
-  </si>
-  <si>
     <t>ShieldEntryModal</t>
   </si>
   <si>
@@ -1791,6 +1791,30 @@
     <t>../../../components/multichain/activity-v2/activity-list, ../activity-v2/activity-list</t>
   </si>
   <si>
+    <t>Tag</t>
+  </si>
+  <si>
+    <t>Chip</t>
+  </si>
+  <si>
+    <t>../chip, .</t>
+  </si>
+  <si>
+    <t>RecipientWithAddress</t>
+  </si>
+  <si>
+    <t>../../ui/sender-to-recipient/sender-to-recipient.component</t>
+  </si>
+  <si>
+    <t>Option</t>
+  </si>
+  <si>
+    <t>MultichainAddressRow</t>
+  </si>
+  <si>
+    <t>../multichain-address-row/multichain-address-row</t>
+  </si>
+  <si>
     <t>MultichainSiteCellTooltip</t>
   </si>
   <si>
@@ -1803,12 +1827,6 @@
     <t>../../multichain/edit-networks-modal, ../../..</t>
   </si>
   <si>
-    <t>MultichainAddressRow</t>
-  </si>
-  <si>
-    <t>../multichain-address-row/multichain-address-row</t>
-  </si>
-  <si>
     <t>MultichainHoveredAddressRowsList</t>
   </si>
   <si>
@@ -1821,22 +1839,64 @@
     <t>../../app/modals/hold-to-reveal-modal/hold-to-reveal-modal</t>
   </si>
   <si>
-    <t>Tag</t>
-  </si>
-  <si>
-    <t>Chip</t>
-  </si>
-  <si>
-    <t>../chip, .</t>
-  </si>
-  <si>
-    <t>RecipientWithAddress</t>
-  </si>
-  <si>
-    <t>../../ui/sender-to-recipient/sender-to-recipient.component</t>
-  </si>
-  <si>
-    <t>Option</t>
+    <t>PercentageChange</t>
+  </si>
+  <si>
+    <t>./price/percentage-change/percentage-change, ../../../../multichain/token-list-item/price/percentage-change</t>
+  </si>
+  <si>
+    <t>SnapUIMarkdown</t>
+  </si>
+  <si>
+    <t>../../app/snaps/snap-ui-markdown, ../../../../components/app/snaps/snap-ui-markdown</t>
+  </si>
+  <si>
+    <t>SelectRpcUrlModal</t>
+  </si>
+  <si>
+    <t>../network-list-menu/select-rpc-url-modal/select-rpc-url-modal, ./select-rpc-url-modal/select-rpc-url-modal</t>
+  </si>
+  <si>
+    <t>NetworksForm</t>
+  </si>
+  <si>
+    <t>../../../pages/settings/networks-tab/networks-form, ../../../../../pages/settings/networks-tab/networks-form/networks-form</t>
+  </si>
+  <si>
+    <t>ShowHideToggle</t>
+  </si>
+  <si>
+    <t>../../ui/show-hide-toggle</t>
+  </si>
+  <si>
+    <t>NotificationsTagCounter</t>
+  </si>
+  <si>
+    <t>../notifications-tag-counter</t>
+  </si>
+  <si>
+    <t>StackCard</t>
+  </si>
+  <si>
+    <t>./stack-card</t>
+  </si>
+  <si>
+    <t>StackCardEmpty</t>
+  </si>
+  <si>
+    <t>./stack-card-empty</t>
+  </si>
+  <si>
+    <t>Carousel</t>
+  </si>
+  <si>
+    <t>./carousel</t>
+  </si>
+  <si>
+    <t>LegacyActivityListItem</t>
+  </si>
+  <si>
+    <t>../activity-list-item</t>
   </si>
   <si>
     <t>CoinOverview</t>
@@ -1863,12 +1923,6 @@
     <t>../../../pages/confirmations/components/edit-gas-popover</t>
   </si>
   <si>
-    <t>ShowHideToggle</t>
-  </si>
-  <si>
-    <t>../../ui/show-hide-toggle</t>
-  </si>
-  <si>
     <t>PerpsSectionSkeleton</t>
   </si>
   <si>
@@ -1920,60 +1974,6 @@
     <t>../app-loading-spinner, ../../../../components/app/app-loading-spinner</t>
   </si>
   <si>
-    <t>PercentageChange</t>
-  </si>
-  <si>
-    <t>./price/percentage-change/percentage-change, ../../../../multichain/token-list-item/price/percentage-change</t>
-  </si>
-  <si>
-    <t>SnapUIMarkdown</t>
-  </si>
-  <si>
-    <t>../../app/snaps/snap-ui-markdown, ../../../../components/app/snaps/snap-ui-markdown</t>
-  </si>
-  <si>
-    <t>SelectRpcUrlModal</t>
-  </si>
-  <si>
-    <t>../network-list-menu/select-rpc-url-modal/select-rpc-url-modal, ./select-rpc-url-modal/select-rpc-url-modal</t>
-  </si>
-  <si>
-    <t>NetworksForm</t>
-  </si>
-  <si>
-    <t>../../../pages/settings/networks-tab/networks-form, ../../../../../pages/settings/networks-tab/networks-form/networks-form</t>
-  </si>
-  <si>
-    <t>NotificationsTagCounter</t>
-  </si>
-  <si>
-    <t>../notifications-tag-counter</t>
-  </si>
-  <si>
-    <t>StackCard</t>
-  </si>
-  <si>
-    <t>./stack-card</t>
-  </si>
-  <si>
-    <t>StackCardEmpty</t>
-  </si>
-  <si>
-    <t>./stack-card-empty</t>
-  </si>
-  <si>
-    <t>Carousel</t>
-  </si>
-  <si>
-    <t>./carousel</t>
-  </si>
-  <si>
-    <t>LegacyActivityListItem</t>
-  </si>
-  <si>
-    <t>../activity-list-item</t>
-  </si>
-  <si>
     <t>DropdownEditor</t>
   </si>
   <si>
@@ -2043,6 +2043,24 @@
     <t>../../../multichain/disconnect-all-modal/disconnect-all-modal, ../../disconnect-all-modal/disconnect-all-modal</t>
   </si>
   <si>
+    <t>PermissionListItem</t>
+  </si>
+  <si>
+    <t>./components/permission-list-item</t>
+  </si>
+  <si>
+    <t>AssetComponent</t>
+  </si>
+  <si>
+    <t>./Asset, ../../UI/asset</t>
+  </si>
+  <si>
+    <t>OnboardingIntroStep</t>
+  </si>
+  <si>
+    <t>./OnboardingIntroStep</t>
+  </si>
+  <si>
     <t>Copyable</t>
   </si>
   <si>
@@ -2055,12 +2073,6 @@
     <t>../snap-version/snap-external-pill</t>
   </si>
   <si>
-    <t>OnboardingIntroStep</t>
-  </si>
-  <si>
-    <t>./OnboardingIntroStep</t>
-  </si>
-  <si>
     <t>WhatArePerpsStep</t>
   </si>
   <si>
@@ -2091,18 +2103,6 @@
     <t>../asset-list/cells/generic-asset-cell-layout, ../../asset-list/cells/generic-asset-cell-layout</t>
   </si>
   <si>
-    <t>PermissionListItem</t>
-  </si>
-  <si>
-    <t>./components/permission-list-item</t>
-  </si>
-  <si>
-    <t>AssetComponent</t>
-  </si>
-  <si>
-    <t>./Asset, ../../UI/asset</t>
-  </si>
-  <si>
     <t>CustomAmountSkeleton</t>
   </si>
   <si>
@@ -2115,6 +2115,12 @@
     <t>../../info-popover-tooltip</t>
   </si>
   <si>
+    <t>CustomAmountInfoSkeleton</t>
+  </si>
+  <si>
+    <t>../../info/custom-amount-info</t>
+  </si>
+  <si>
     <t>PayWithRowSkeleton</t>
   </si>
   <si>
@@ -2127,12 +2133,6 @@
     <t>../custom-amount-info, ../../../info/custom-amount-info</t>
   </si>
   <si>
-    <t>CustomAmountInfoSkeleton</t>
-  </si>
-  <si>
-    <t>../../info/custom-amount-info</t>
-  </si>
-  <si>
     <t>TitleSkeleton</t>
   </si>
   <si>
@@ -2142,31 +2142,31 @@
     <t>../../../../../components/app/confirm/info/row, ../../../../../../../components/app/confirm/info/row</t>
   </si>
   <si>
+    <t>PageFooter</t>
+  </si>
+  <si>
+    <t>../../../../../components/multichain/pages/page</t>
+  </si>
+  <si>
     <t>SimpleHeaderLayout</t>
   </si>
   <si>
-    <t>PageFooter</t>
-  </si>
-  <si>
-    <t>../../../../../components/multichain/pages/page</t>
-  </si>
-  <si>
     <t>TransactionDetails</t>
   </si>
   <si>
     <t>../transaction-details, ../shared/transaction-details/transaction-details</t>
   </si>
   <si>
+    <t>SiteCellTooltip</t>
+  </si>
+  <si>
+    <t>./site-cell-tooltip</t>
+  </si>
+  <si>
     <t>AssetCellTitle</t>
   </si>
   <si>
     <t>../../asset-list/cells/asset-title</t>
-  </si>
-  <si>
-    <t>SiteCellTooltip</t>
-  </si>
-  <si>
-    <t>./site-cell-tooltip</t>
   </si>
   <si>
     <t>Delineator</t>
@@ -3154,10 +3154,10 @@
         <v>6</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E22" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F22" t="s">
         <v>16</v>
@@ -3177,10 +3177,10 @@
         <v>6</v>
       </c>
       <c r="D23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E23" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F23" t="s">
         <v>16</v>
@@ -3384,7 +3384,7 @@
         <v>4</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -3407,10 +3407,10 @@
         <v>4</v>
       </c>
       <c r="D33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E33" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F33" t="s">
         <v>12</v>
@@ -3433,10 +3433,10 @@
         <v>3</v>
       </c>
       <c r="E34" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F34" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G34" t="s">
         <v>81</v>
@@ -3456,10 +3456,10 @@
         <v>4</v>
       </c>
       <c r="E35" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F35" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G35" t="s">
         <v>83</v>
@@ -3686,10 +3686,10 @@
         <v>3</v>
       </c>
       <c r="E45" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F45" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G45" t="s">
         <v>103</v>
@@ -3709,10 +3709,10 @@
         <v>3</v>
       </c>
       <c r="E46" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F46" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G46" t="s">
         <v>105</v>
@@ -3732,10 +3732,10 @@
         <v>2</v>
       </c>
       <c r="E47" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G47" t="s">
         <v>107</v>
@@ -3752,13 +3752,13 @@
         <v>3</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E48" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F48" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G48" t="s">
         <v>109</v>
@@ -3778,7 +3778,7 @@
         <v>3</v>
       </c>
       <c r="E49" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F49" t="s">
         <v>12</v>
@@ -3798,7 +3798,7 @@
         <v>3</v>
       </c>
       <c r="D50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" t="s">
         <v>11</v>
@@ -4422,7 +4422,7 @@
         <v>2</v>
       </c>
       <c r="E77" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="F77" t="s">
         <v>12</v>
@@ -4442,16 +4442,16 @@
         <v>2</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F78" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G78" t="s">
-        <v>57</v>
+        <v>166</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -4459,7 +4459,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C79">
         <v>2</v>
@@ -4468,13 +4468,13 @@
         <v>2</v>
       </c>
       <c r="E79" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F79" t="s">
         <v>12</v>
       </c>
       <c r="G79" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -4482,13 +4482,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C80">
         <v>2</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E80" t="s">
         <v>11</v>
@@ -4497,7 +4497,7 @@
         <v>12</v>
       </c>
       <c r="G80" t="s">
-        <v>169</v>
+        <v>57</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -4537,10 +4537,10 @@
         <v>2</v>
       </c>
       <c r="E82" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F82" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G82" t="s">
         <v>173</v>
@@ -4560,13 +4560,13 @@
         <v>1</v>
       </c>
       <c r="E83" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F83" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G83" t="s">
-        <v>57</v>
+        <v>175</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -4574,22 +4574,22 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C84">
         <v>2</v>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F84" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G84" t="s">
-        <v>57</v>
+        <v>177</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -4597,7 +4597,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C85">
         <v>2</v>
@@ -4606,13 +4606,13 @@
         <v>2</v>
       </c>
       <c r="E85" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="F85" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G85" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -4620,22 +4620,22 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C86">
         <v>2</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F86" t="s">
         <v>12</v>
       </c>
       <c r="G86" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -4643,22 +4643,22 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C87">
         <v>2</v>
       </c>
       <c r="D87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F87" t="s">
         <v>12</v>
       </c>
       <c r="G87" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4666,7 +4666,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C88">
         <v>2</v>
@@ -4675,13 +4675,13 @@
         <v>2</v>
       </c>
       <c r="E88" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F88" t="s">
         <v>12</v>
       </c>
       <c r="G88" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4689,7 +4689,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C89">
         <v>2</v>
@@ -4698,13 +4698,13 @@
         <v>2</v>
       </c>
       <c r="E89" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="F89" t="s">
         <v>12</v>
       </c>
       <c r="G89" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -4712,22 +4712,22 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C90">
         <v>2</v>
       </c>
       <c r="D90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E90" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="F90" t="s">
         <v>12</v>
       </c>
       <c r="G90" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -4735,22 +4735,22 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C91">
         <v>2</v>
       </c>
       <c r="D91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E91" t="s">
         <v>15</v>
       </c>
       <c r="F91" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G91" t="s">
-        <v>189</v>
+        <v>57</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -4758,22 +4758,22 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C92">
         <v>2</v>
       </c>
       <c r="D92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F92" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G92" t="s">
-        <v>191</v>
+        <v>57</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -4790,10 +4790,10 @@
         <v>2</v>
       </c>
       <c r="E93" t="s">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="F93" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G93" t="s">
         <v>193</v>
@@ -4813,7 +4813,7 @@
         <v>1</v>
       </c>
       <c r="E94" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="F94" t="s">
         <v>12</v>
@@ -4971,10 +4971,10 @@
         <v>2</v>
       </c>
       <c r="D101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E101" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="F101" t="s">
         <v>12</v>
@@ -4994,16 +4994,16 @@
         <v>2</v>
       </c>
       <c r="D102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E102" t="s">
-        <v>211</v>
+        <v>22</v>
       </c>
       <c r="F102" t="s">
         <v>12</v>
       </c>
       <c r="G102" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -5011,16 +5011,16 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
+        <v>212</v>
+      </c>
+      <c r="C103">
+        <v>2</v>
+      </c>
+      <c r="D103">
+        <v>2</v>
+      </c>
+      <c r="E103" t="s">
         <v>213</v>
-      </c>
-      <c r="C103">
-        <v>2</v>
-      </c>
-      <c r="D103">
-        <v>1</v>
-      </c>
-      <c r="E103" t="s">
-        <v>48</v>
       </c>
       <c r="F103" t="s">
         <v>12</v>
@@ -5040,10 +5040,10 @@
         <v>2</v>
       </c>
       <c r="D104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="F104" t="s">
         <v>12</v>
@@ -5072,7 +5072,7 @@
         <v>12</v>
       </c>
       <c r="G105" t="s">
-        <v>57</v>
+        <v>218</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -5080,7 +5080,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C106">
         <v>2</v>
@@ -5089,13 +5089,13 @@
         <v>2</v>
       </c>
       <c r="E106" t="s">
-        <v>211</v>
+        <v>22</v>
       </c>
       <c r="F106" t="s">
         <v>12</v>
       </c>
       <c r="G106" t="s">
-        <v>219</v>
+        <v>57</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -5112,7 +5112,7 @@
         <v>2</v>
       </c>
       <c r="E107" t="s">
-        <v>48</v>
+        <v>213</v>
       </c>
       <c r="F107" t="s">
         <v>12</v>
@@ -5247,16 +5247,16 @@
         <v>2</v>
       </c>
       <c r="D113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E113" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F113" t="s">
         <v>16</v>
       </c>
       <c r="G113" t="s">
-        <v>57</v>
+        <v>233</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -5264,22 +5264,22 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C114">
         <v>2</v>
       </c>
       <c r="D114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E114" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F114" t="s">
         <v>16</v>
       </c>
       <c r="G114" t="s">
-        <v>234</v>
+        <v>57</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -7312,7 +7312,7 @@
         <v>3</v>
       </c>
       <c r="D116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E116" t="s">
         <v>452</v>
@@ -7346,7 +7346,7 @@
         <v>3</v>
       </c>
       <c r="D118">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E118" t="s">
         <v>456</v>
@@ -7380,7 +7380,7 @@
         <v>3</v>
       </c>
       <c r="D120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E120" t="s">
         <v>460</v>
@@ -7431,7 +7431,7 @@
         <v>3</v>
       </c>
       <c r="D123">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E123" t="s">
         <v>466</v>
@@ -7669,7 +7669,7 @@
         <v>3</v>
       </c>
       <c r="D137">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E137" t="s">
         <v>492</v>
@@ -7720,7 +7720,7 @@
         <v>3</v>
       </c>
       <c r="D140">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E140" t="s">
         <v>498</v>
@@ -8570,10 +8570,10 @@
         <v>2</v>
       </c>
       <c r="D190">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E190" t="s">
-        <v>593</v>
+        <v>57</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
@@ -8581,16 +8581,16 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
+        <v>593</v>
+      </c>
+      <c r="C191">
+        <v>2</v>
+      </c>
+      <c r="D191">
+        <v>2</v>
+      </c>
+      <c r="E191" t="s">
         <v>594</v>
-      </c>
-      <c r="C191">
-        <v>2</v>
-      </c>
-      <c r="D191">
-        <v>2</v>
-      </c>
-      <c r="E191" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
@@ -8598,16 +8598,16 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
+        <v>595</v>
+      </c>
+      <c r="C192">
+        <v>2</v>
+      </c>
+      <c r="D192">
+        <v>2</v>
+      </c>
+      <c r="E192" t="s">
         <v>596</v>
-      </c>
-      <c r="C192">
-        <v>2</v>
-      </c>
-      <c r="D192">
-        <v>2</v>
-      </c>
-      <c r="E192" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
@@ -8615,16 +8615,16 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C193">
         <v>2</v>
       </c>
       <c r="D193">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E193" t="s">
-        <v>599</v>
+        <v>57</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
@@ -8632,7 +8632,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C194">
         <v>2</v>
@@ -8641,7 +8641,7 @@
         <v>2</v>
       </c>
       <c r="E194" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
@@ -8649,16 +8649,16 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C195">
         <v>2</v>
       </c>
       <c r="D195">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E195" t="s">
-        <v>57</v>
+        <v>601</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
@@ -8666,16 +8666,16 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
+        <v>602</v>
+      </c>
+      <c r="C196">
+        <v>2</v>
+      </c>
+      <c r="D196">
+        <v>2</v>
+      </c>
+      <c r="E196" t="s">
         <v>603</v>
-      </c>
-      <c r="C196">
-        <v>2</v>
-      </c>
-      <c r="D196">
-        <v>2</v>
-      </c>
-      <c r="E196" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
@@ -8683,16 +8683,16 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
+        <v>604</v>
+      </c>
+      <c r="C197">
+        <v>2</v>
+      </c>
+      <c r="D197">
+        <v>2</v>
+      </c>
+      <c r="E197" t="s">
         <v>605</v>
-      </c>
-      <c r="C197">
-        <v>2</v>
-      </c>
-      <c r="D197">
-        <v>2</v>
-      </c>
-      <c r="E197" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
@@ -8700,16 +8700,16 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
+        <v>606</v>
+      </c>
+      <c r="C198">
+        <v>2</v>
+      </c>
+      <c r="D198">
+        <v>2</v>
+      </c>
+      <c r="E198" t="s">
         <v>607</v>
-      </c>
-      <c r="C198">
-        <v>2</v>
-      </c>
-      <c r="D198">
-        <v>1</v>
-      </c>
-      <c r="E198" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
@@ -8774,7 +8774,7 @@
         <v>2</v>
       </c>
       <c r="D202">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E202" t="s">
         <v>615</v>
@@ -8808,7 +8808,7 @@
         <v>2</v>
       </c>
       <c r="D204">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E204" t="s">
         <v>619</v>
@@ -8825,7 +8825,7 @@
         <v>2</v>
       </c>
       <c r="D205">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E205" t="s">
         <v>621</v>
@@ -8842,10 +8842,10 @@
         <v>2</v>
       </c>
       <c r="D206">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E206" t="s">
-        <v>57</v>
+        <v>623</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
@@ -8853,16 +8853,16 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C207">
         <v>2</v>
       </c>
       <c r="D207">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E207" t="s">
-        <v>57</v>
+        <v>625</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
@@ -8870,16 +8870,16 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C208">
         <v>2</v>
       </c>
       <c r="D208">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E208" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
@@ -8887,7 +8887,7 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C209">
         <v>2</v>
@@ -8896,7 +8896,7 @@
         <v>2</v>
       </c>
       <c r="E209" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
@@ -8904,16 +8904,16 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C210">
         <v>2</v>
       </c>
       <c r="D210">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E210" t="s">
-        <v>57</v>
+        <v>631</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
@@ -8921,7 +8921,7 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C211">
         <v>2</v>
@@ -8930,7 +8930,7 @@
         <v>2</v>
       </c>
       <c r="E211" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
@@ -8938,7 +8938,7 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C212">
         <v>2</v>
@@ -8947,7 +8947,7 @@
         <v>1</v>
       </c>
       <c r="E212" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
@@ -8955,16 +8955,16 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C213">
         <v>2</v>
       </c>
       <c r="D213">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E213" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
@@ -8972,7 +8972,7 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C214">
         <v>2</v>
@@ -8981,7 +8981,7 @@
         <v>2</v>
       </c>
       <c r="E214" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -8989,16 +8989,16 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C215">
         <v>2</v>
       </c>
       <c r="D215">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E215" t="s">
-        <v>638</v>
+        <v>57</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
@@ -9006,16 +9006,16 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C216">
         <v>2</v>
       </c>
       <c r="D216">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E216" t="s">
-        <v>640</v>
+        <v>57</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
@@ -9023,7 +9023,7 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C217">
         <v>2</v>
@@ -9032,7 +9032,7 @@
         <v>2</v>
       </c>
       <c r="E217" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
@@ -9040,7 +9040,7 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C218">
         <v>2</v>
@@ -9049,7 +9049,7 @@
         <v>2</v>
       </c>
       <c r="E218" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
@@ -9057,7 +9057,7 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C219">
         <v>2</v>
@@ -9066,7 +9066,7 @@
         <v>1</v>
       </c>
       <c r="E219" t="s">
-        <v>646</v>
+        <v>57</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
@@ -9097,7 +9097,7 @@
         <v>2</v>
       </c>
       <c r="D221">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E221" t="s">
         <v>650</v>
@@ -9114,7 +9114,7 @@
         <v>2</v>
       </c>
       <c r="D222">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E222" t="s">
         <v>652</v>
@@ -9369,7 +9369,7 @@
         <v>2</v>
       </c>
       <c r="D237">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E237" t="s">
         <v>677</v>
@@ -9420,7 +9420,7 @@
         <v>2</v>
       </c>
       <c r="D240">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E240" t="s">
         <v>683</v>
@@ -9454,7 +9454,7 @@
         <v>2</v>
       </c>
       <c r="D242">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E242" t="s">
         <v>687</v>
@@ -9505,7 +9505,7 @@
         <v>2</v>
       </c>
       <c r="D245">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E245" t="s">
         <v>693</v>
@@ -9658,10 +9658,10 @@
         <v>2</v>
       </c>
       <c r="D254">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E254" t="s">
-        <v>57</v>
+        <v>710</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
@@ -9669,16 +9669,16 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C255">
         <v>2</v>
       </c>
       <c r="D255">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E255" t="s">
-        <v>711</v>
+        <v>57</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
@@ -9709,7 +9709,7 @@
         <v>2</v>
       </c>
       <c r="D257">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E257" t="s">
         <v>715</v>
@@ -9726,7 +9726,7 @@
         <v>2</v>
       </c>
       <c r="D258">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E258" t="s">
         <v>717</v>
@@ -9971,7 +9971,7 @@
         <v>743</v>
       </c>
       <c r="B5">
-        <v>9014</v>
+        <v>9015</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -9979,7 +9979,7 @@
         <v>744</v>
       </c>
       <c r="B6">
-        <v>1935</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
